--- a/survey_templates/034_oedipus_rex_knowledge_quiz--survey_templates.xlsx
+++ b/survey_templates/034_oedipus_rex_knowledge_quiz--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -748,7 +748,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Reading Group</t>
+          <t>Reading Group Answer</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -794,7 +794,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Class</t>
+          <t>Class Answer</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -840,7 +840,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tutor</t>
+          <t>Tutor Answer</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -886,7 +886,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Submission</t>
+          <t>Submission Answer</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -932,7 +932,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Teacher</t>
+          <t>Teacher Answer</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -978,7 +978,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>School Answer</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Student</t>
+          <t>Student Answer</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
